--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jul-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13977,7 +13977,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14221,7 +14221,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15319,7 +15319,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16722,7 +16722,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16905,7 +16905,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17271,7 +17271,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17393,7 +17393,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17820,7 +17820,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18857,7 +18857,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19101,7 +19101,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19162,7 +19162,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19833,7 +19833,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20077,7 +20077,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20382,7 +20382,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20565,7 +20565,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20626,7 +20626,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20809,7 +20809,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21602,7 +21602,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21785,7 +21785,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22273,7 +22273,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22761,7 +22761,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23005,7 +23005,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23188,7 +23188,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23310,7 +23310,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23432,7 +23432,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23554,7 +23554,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23615,7 +23615,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23737,7 +23737,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23798,7 +23798,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23859,7 +23859,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24042,7 +24042,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24225,7 +24225,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24408,7 +24408,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24530,7 +24530,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24652,7 +24652,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24835,7 +24835,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24957,7 +24957,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25262,7 +25262,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25445,7 +25445,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25689,7 +25689,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25994,7 +25994,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26238,7 +26238,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26299,7 +26299,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26360,7 +26360,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26421,7 +26421,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26665,7 +26665,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26909,7 +26909,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26970,7 +26970,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27275,7 +27275,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27397,7 +27397,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27458,7 +27458,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27702,7 +27702,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27763,7 +27763,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28129,7 +28129,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28190,7 +28190,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28251,7 +28251,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28312,7 +28312,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28739,7 +28739,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28983,7 +28983,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29166,7 +29166,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29471,7 +29471,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29593,7 +29593,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29715,7 +29715,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29837,7 +29837,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29959,7 +29959,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30081,7 +30081,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30325,7 +30325,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30508,7 +30508,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30569,7 +30569,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30813,7 +30813,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30874,7 +30874,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30935,7 +30935,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31118,7 +31118,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31240,7 +31240,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31301,7 +31301,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31362,7 +31362,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31423,7 +31423,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31484,7 +31484,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31545,7 +31545,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31606,7 +31606,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31667,7 +31667,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31728,7 +31728,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31911,7 +31911,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32033,7 +32033,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32155,7 +32155,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32399,7 +32399,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32643,7 +32643,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32765,7 +32765,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32887,7 +32887,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33192,7 +33192,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33253,7 +33253,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33314,7 +33314,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33375,7 +33375,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33558,7 +33558,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33741,7 +33741,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33802,7 +33802,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34229,7 +34229,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34351,7 +34351,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34717,7 +34717,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34839,7 +34839,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34900,7 +34900,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34961,7 +34961,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35144,7 +35144,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35266,7 +35266,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35449,7 +35449,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35571,7 +35571,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35693,7 +35693,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35876,7 +35876,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36059,7 +36059,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36181,7 +36181,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36364,7 +36364,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36425,7 +36425,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36486,7 +36486,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36547,7 +36547,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36730,7 +36730,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36852,7 +36852,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -37096,7 +37096,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37279,7 +37279,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37767,7 +37767,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37828,7 +37828,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37950,7 +37950,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38011,7 +38011,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38072,7 +38072,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38255,7 +38255,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38316,7 +38316,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38438,7 +38438,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38560,7 +38560,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38682,7 +38682,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38743,7 +38743,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38804,7 +38804,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38926,7 +38926,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -39109,7 +39109,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39170,7 +39170,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39231,7 +39231,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39353,7 +39353,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39414,7 +39414,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39536,7 +39536,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39597,7 +39597,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39658,7 +39658,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39719,7 +39719,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39780,7 +39780,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39841,7 +39841,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -40024,7 +40024,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40085,7 +40085,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40146,7 +40146,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40207,7 +40207,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40268,7 +40268,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40329,7 +40329,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40390,7 +40390,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40512,7 +40512,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40573,7 +40573,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40634,7 +40634,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40695,7 +40695,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40756,7 +40756,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40878,7 +40878,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41061,7 +41061,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41122,7 +41122,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41183,7 +41183,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41244,7 +41244,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41305,7 +41305,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41427,7 +41427,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41488,7 +41488,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41610,7 +41610,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41671,7 +41671,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41732,7 +41732,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41793,7 +41793,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41854,7 +41854,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41915,7 +41915,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41976,7 +41976,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42037,7 +42037,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42220,7 +42220,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42281,7 +42281,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42342,7 +42342,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42403,7 +42403,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42464,7 +42464,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42525,7 +42525,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42586,7 +42586,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42769,7 +42769,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42830,7 +42830,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42891,7 +42891,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42952,7 +42952,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43013,7 +43013,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43074,7 +43074,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43135,7 +43135,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43196,7 +43196,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43318,7 +43318,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43379,7 +43379,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43440,7 +43440,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43501,7 +43501,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43562,7 +43562,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43623,7 +43623,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43684,7 +43684,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43745,7 +43745,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43806,7 +43806,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43867,7 +43867,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -43928,7 +43928,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -43989,7 +43989,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44050,7 +44050,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44172,7 +44172,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44233,7 +44233,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44294,7 +44294,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44477,7 +44477,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44538,7 +44538,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -44599,7 +44599,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -44660,7 +44660,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44721,7 +44721,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44782,7 +44782,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -44843,7 +44843,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -44904,7 +44904,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -44965,7 +44965,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45087,7 +45087,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45148,7 +45148,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45209,7 +45209,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45331,7 +45331,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45392,7 +45392,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45575,7 +45575,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -45636,7 +45636,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45697,7 +45697,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45758,7 +45758,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45819,7 +45819,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -45880,7 +45880,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -45941,7 +45941,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -46063,7 +46063,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46124,7 +46124,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46185,7 +46185,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46246,7 +46246,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46307,7 +46307,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46429,7 +46429,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -46490,7 +46490,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2025.xlsx
@@ -867,7 +867,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1054,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1180,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1306,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1432,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1741,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2111,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2176,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2302,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2489,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2554,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2741,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2867,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2993,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3119,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3554,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3619,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3806,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3871,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4184,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4249,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4497,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4470,7 +4562,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +4932,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4897,7 +4997,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5184,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5141,7 +5249,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5497,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5623,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5688,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5818,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +5883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6009,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5934,7 +6074,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6200,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6265,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6391,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6361,7 +6521,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6586,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6773,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +6899,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6914,7 +7090,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7036,7 +7216,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7097,7 +7281,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7158,7 +7346,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7402,7 +7594,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7524,7 +7720,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7585,7 +7785,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7707,7 +7911,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7829,7 +8037,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7890,7 +8102,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7951,7 +8167,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8073,7 +8293,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8134,7 +8358,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8195,7 +8423,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8256,7 +8488,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8317,7 +8553,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8439,7 +8679,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8561,7 +8805,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8683,7 +8931,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8744,7 +8996,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8988,7 +9244,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9171,7 +9431,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9415,7 +9679,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9537,7 +9805,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9598,7 +9870,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9659,7 +9935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9842,7 +10122,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9903,7 +10187,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9964,7 +10252,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10086,7 +10378,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10330,7 +10626,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10452,7 +10752,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10513,7 +10817,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10574,7 +10882,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10635,7 +10947,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10940,7 +11256,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11123,7 +11443,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11306,7 +11630,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11367,7 +11695,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11489,7 +11821,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11550,7 +11886,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11672,7 +12012,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11733,7 +12077,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11855,7 +12203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11977,7 +12329,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12099,7 +12455,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12343,7 +12703,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12404,7 +12768,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12465,7 +12833,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12587,7 +12959,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12709,7 +13085,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12770,7 +13150,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12892,7 +13276,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13136,7 +13524,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13197,7 +13589,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13319,7 +13715,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13380,7 +13780,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13563,7 +13967,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13624,7 +14032,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13685,7 +14097,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13746,7 +14162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13807,7 +14227,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13929,7 +14353,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14051,7 +14479,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14112,7 +14544,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14173,7 +14609,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14295,7 +14735,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14417,7 +14861,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14600,7 +15048,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14661,7 +15113,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14722,7 +15178,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14844,7 +15304,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15149,7 +15613,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15210,7 +15678,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15454,7 +15926,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15637,7 +16113,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15698,7 +16178,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16003,7 +16487,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16064,7 +16552,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16247,7 +16739,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16308,7 +16804,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16491,7 +16991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16552,7 +17056,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16796,7 +17304,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16918,7 +17430,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16979,7 +17495,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17040,7 +17560,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17101,7 +17625,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17284,7 +17812,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17528,7 +18060,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18125,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +18251,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17772,7 +18316,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17955,7 +18503,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18016,7 +18568,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18138,7 +18694,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18260,7 +18820,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18382,7 +18946,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18443,7 +19011,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18504,7 +19076,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18565,7 +19141,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18687,7 +19267,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18870,7 +19454,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18931,7 +19519,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19175,7 +19767,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19297,7 +19893,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19480,7 +20080,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19602,7 +20206,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19663,7 +20271,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19724,7 +20336,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19785,7 +20401,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19846,7 +20466,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +20653,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20090,7 +20718,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20151,7 +20783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20273,7 +20909,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20578,7 +21218,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20700,7 +21344,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20761,7 +21409,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21005,7 +21657,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21066,7 +21722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21188,7 +21848,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21249,7 +21913,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21371,7 +22039,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +22104,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21554,7 +22230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21676,7 +22356,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21737,7 +22421,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21859,7 +22547,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21981,7 +22673,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22042,7 +22738,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +22803,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22164,7 +22868,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22225,7 +22933,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22286,7 +22998,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22347,7 +23063,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22408,7 +23128,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22469,7 +23193,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22530,7 +23258,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +23323,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22713,7 +23449,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22774,7 +23514,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22957,7 +23701,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23018,7 +23766,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23140,7 +23892,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23201,7 +23957,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23262,7 +24022,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23445,7 +24209,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23506,7 +24274,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23628,7 +24400,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23750,7 +24526,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23811,7 +24591,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23872,7 +24656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23933,7 +24721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23994,7 +24786,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24116,7 +24912,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24238,7 +25038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24299,7 +25103,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24360,7 +25168,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24482,7 +25294,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24543,7 +25359,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24604,7 +25424,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24665,7 +25489,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24787,7 +25615,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +25741,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25031,7 +25867,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25092,7 +25932,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25275,7 +26119,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25336,7 +26184,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25397,7 +26249,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25458,7 +26314,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25519,7 +26379,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25580,7 +26444,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25702,7 +26570,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25763,7 +26635,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25885,7 +26761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25946,7 +26826,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26068,7 +26952,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26190,7 +27078,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26251,7 +27143,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26434,7 +27330,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26678,7 +27578,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26739,7 +27643,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27044,7 +27952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27288,7 +28200,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27349,7 +28265,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27410,7 +28330,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27532,7 +28456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27776,7 +28704,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27837,7 +28769,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28081,7 +29017,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28264,7 +29204,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28447,7 +29391,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28569,7 +29517,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28691,7 +29643,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28813,7 +29769,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28874,7 +29834,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29057,7 +30021,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29118,7 +30086,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29301,7 +30273,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29362,7 +30338,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29423,7 +30403,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29484,7 +30468,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29606,7 +30594,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29667,7 +30659,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29728,7 +30724,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29789,7 +30789,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29911,7 +30915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30033,7 +31041,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30216,7 +31228,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30277,7 +31293,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30399,7 +31419,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30460,7 +31484,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30521,7 +31549,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30582,7 +31614,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30643,7 +31679,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30826,7 +31866,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30948,7 +31992,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31009,7 +32057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31192,7 +32244,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31253,7 +32309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31375,7 +32435,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31497,7 +32561,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31619,7 +32687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31741,7 +32813,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31802,7 +32878,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31863,7 +32943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32168,7 +33252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32290,7 +33378,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32351,7 +33443,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32473,7 +33569,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32534,7 +33634,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32595,7 +33699,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32656,7 +33764,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32778,7 +33890,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32839,7 +33955,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33022,7 +34142,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33144,7 +34268,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33205,7 +34333,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33327,7 +34459,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33571,7 +34707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33632,7 +34772,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33693,7 +34837,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33754,7 +34902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33815,7 +34967,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33876,7 +35032,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33937,7 +35097,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34059,7 +35223,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34242,7 +35410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34303,7 +35475,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34425,7 +35601,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34547,7 +35727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34608,7 +35792,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34669,7 +35857,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34791,7 +35983,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34852,7 +36048,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34974,7 +36174,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35035,7 +36239,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35096,7 +36304,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35218,7 +36430,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35401,7 +36617,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35584,7 +36804,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35645,7 +36869,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35706,7 +36934,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35767,7 +36999,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35828,7 +37064,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36011,7 +37251,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36072,7 +37316,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36316,7 +37564,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36377,7 +37629,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36438,7 +37694,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36499,7 +37759,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36560,7 +37824,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36621,7 +37889,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36804,7 +38076,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36865,7 +38141,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36926,7 +38206,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37048,7 +38332,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +38397,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37414,7 +38706,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37536,7 +38832,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37597,7 +38897,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37658,7 +38962,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37719,7 +39027,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37780,7 +39092,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37902,7 +39218,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37963,7 +39283,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38024,7 +39348,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38146,7 +39474,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38207,7 +39539,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38268,7 +39604,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38329,7 +39669,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38390,7 +39734,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38451,7 +39799,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38512,7 +39864,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38573,7 +39929,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38634,7 +39994,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38817,7 +40181,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38878,7 +40246,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38939,7 +40311,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39183,7 +40559,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39305,7 +40685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39366,7 +40750,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39549,7 +40937,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39671,7 +41063,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39793,7 +41189,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39915,7 +41315,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40037,7 +41441,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40098,7 +41506,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40220,7 +41632,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40342,7 +41758,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40464,7 +41884,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40525,7 +41949,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40586,7 +42014,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +42140,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40891,7 +42327,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +42453,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41074,7 +42518,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41135,7 +42583,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41196,7 +42648,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41257,7 +42713,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41318,7 +42778,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41440,7 +42904,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41501,7 +42969,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41562,7 +43034,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +43099,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41867,7 +43347,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41928,7 +43412,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41989,7 +43477,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42050,7 +43542,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42111,7 +43607,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42233,7 +43733,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42294,7 +43798,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42416,7 +43924,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42660,7 +44172,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42782,7 +44298,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42904,7 +44424,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42965,7 +44489,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43087,7 +44615,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43148,7 +44680,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43331,7 +44867,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43392,7 +44932,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43514,7 +45058,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43636,7 +45184,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43697,7 +45249,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43819,7 +45375,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43880,7 +45440,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43941,7 +45505,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44002,7 +45570,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44063,7 +45635,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44307,7 +45883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44368,7 +45948,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44490,7 +46074,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44551,7 +46139,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44673,7 +46265,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44917,7 +46513,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44978,7 +46578,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45222,7 +46826,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45283,7 +46891,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45405,7 +47017,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +47082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45527,7 +47147,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45832,7 +47456,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45893,7 +47521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46015,7 +47647,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46076,7 +47712,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46137,7 +47777,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46198,7 +47842,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46320,7 +47968,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46381,7 +48033,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46442,7 +48098,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46503,7 +48163,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jul-2025.xlsx
@@ -684,7 +684,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +997,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1497,7 +1505,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1680,7 +1692,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1989,7 +2005,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2050,7 +2070,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2680,7 +2704,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3184,7 +3212,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3245,7 +3277,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3493,7 +3529,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3745,7 +3785,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4314,7 +4358,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5123,7 +5171,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5314,7 +5366,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5436,7 +5492,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5562,7 +5622,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6139,7 +6203,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7411,7 +7479,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7533,7 +7605,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7976,7 +8052,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9370,7 +9450,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9557,7 +9641,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9744,7 +9832,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10504,7 +10596,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10565,7 +10661,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11073,7 +11173,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12142,7 +12246,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12394,7 +12502,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14292,7 +14404,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14926,7 +15042,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16052,7 +16172,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18381,7 +18505,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20848,7 +20976,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21535,7 +21667,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22169,7 +22305,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23640,7 +23780,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24465,7 +24609,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26058,7 +26206,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26700,7 +26852,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28895,7 +29051,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29960,7 +30120,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30533,7 +30697,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31744,7 +31912,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31805,7 +31977,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32122,7 +32298,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32500,7 +32680,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32752,7 +32936,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33069,7 +33257,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34207,7 +34399,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +36691,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38771,7 +38971,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39413,7 +39617,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40059,7 +40267,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40437,7 +40649,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41128,7 +41344,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41571,7 +41791,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41697,7 +41921,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42205,7 +42433,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42392,7 +42624,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42843,7 +43079,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43225,7 +43465,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43672,7 +43916,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43989,7 +44237,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44050,7 +44302,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44237,7 +44493,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44554,7 +44814,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45761,7 +46025,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45822,7 +46090,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46013,7 +46285,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46204,7 +46480,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46956,7 +47236,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47273,7 +47557,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47586,7 +47874,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
